--- a/etf_holdings/2026-09-29_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:34</t>
+          <t>2026-09-29 01:01:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:34</t>
+          <t>2026-09-29 01:01:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:34</t>
+          <t>2026-09-29 01:01:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:36</t>
+          <t>2026-09-29 01:01:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:36</t>
+          <t>2026-09-29 01:01:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:36</t>
+          <t>2026-09-29 01:01:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:36</t>
+          <t>2026-09-29 01:01:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:36</t>
+          <t>2026-09-29 01:01:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:36</t>
+          <t>2026-09-29 01:01:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:37</t>
+          <t>2026-09-29 01:01:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:37</t>
+          <t>2026-09-29 01:01:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:37</t>
+          <t>2026-09-29 01:01:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:37</t>
+          <t>2026-09-29 01:01:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:37</t>
+          <t>2026-09-29 01:01:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:37</t>
+          <t>2026-09-29 01:01:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:37</t>
+          <t>2026-09-29 01:01:37</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:38</t>
+          <t>2026-09-29 01:01:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:38</t>
+          <t>2026-09-29 01:01:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">

--- a/etf_holdings/2026-09-29_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:34</t>
+          <t>2026-09-29 01:40:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:34</t>
+          <t>2026-09-29 01:40:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:34</t>
+          <t>2026-09-29 01:40:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:35</t>
+          <t>2026-09-29 01:40:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:35</t>
+          <t>2026-09-29 01:40:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:35</t>
+          <t>2026-09-29 01:40:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:35</t>
+          <t>2026-09-29 01:40:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:35</t>
+          <t>2026-09-29 01:40:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:35</t>
+          <t>2026-09-29 01:40:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:38</t>
+          <t>2026-09-29 01:40:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:38</t>
+          <t>2026-09-29 01:40:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">

--- a/etf_holdings/2026-09-29_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:25</t>
+          <t>2026-09-29 22:55:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.93%5285</t>
+          <t>-7.1%4910</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:25</t>
+          <t>2026-09-29 22:55:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.53%1910</t>
+          <t>-3.93%1835</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:25</t>
+          <t>2026-09-29 22:55:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1%2475</t>
+          <t>0%2475</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:27</t>
+          <t>2026-09-29 22:55:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>-2.57%4920</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:27</t>
+          <t>2026-09-29 22:55:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.16%1185</t>
+          <t>-1.69%1165</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:27</t>
+          <t>2026-09-29 22:55:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:27</t>
+          <t>2026-09-29 22:55:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:27</t>
+          <t>2026-09-29 22:55:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:27</t>
+          <t>2026-09-29 22:55:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+2.3%311</t>
+          <t>-5.31%294.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>294.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:28</t>
+          <t>2026-09-29 22:56:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+2.48%1240</t>
+          <t>+2.42%1270</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:28</t>
+          <t>2026-09-29 22:56:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.27%3230</t>
+          <t>+2.32%3305</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>+2.32%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:28</t>
+          <t>2026-09-29 22:56:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.65%5415</t>
+          <t>-4.25%5185</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:28</t>
+          <t>2026-09-29 22:56:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:28</t>
+          <t>2026-09-29 22:56:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,17 +1328,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.29%2295</t>
+          <t>-4.79%2185</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:28</t>
+          <t>2026-09-29 22:56:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:28</t>
+          <t>2026-09-29 22:56:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.1%5670</t>
+          <t>-1.5%5585</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:29</t>
+          <t>2026-09-29 22:56:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1517,17 +1517,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0%2340</t>
+          <t>+4.49%2445</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+4.49%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:29</t>
+          <t>2026-09-29 22:56:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">

--- a/etf_holdings/2026-09-29_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:58</t>
+          <t>2026-09-29 23:06:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:58</t>
+          <t>2026-09-29 23:06:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:58</t>
+          <t>2026-09-29 23:06:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:59</t>
+          <t>2026-09-29 23:06:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:59</t>
+          <t>2026-09-29 23:06:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:59</t>
+          <t>2026-09-29 23:06:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:59</t>
+          <t>2026-09-29 23:06:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:59</t>
+          <t>2026-09-29 23:06:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:59</t>
+          <t>2026-09-29 23:06:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:00</t>
+          <t>2026-09-29 23:06:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:00</t>
+          <t>2026-09-29 23:06:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:00</t>
+          <t>2026-09-29 23:06:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:00</t>
+          <t>2026-09-29 23:06:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:00</t>
+          <t>2026-09-29 23:06:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:00</t>
+          <t>2026-09-29 23:06:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:00</t>
+          <t>2026-09-29 23:06:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:01</t>
+          <t>2026-09-29 23:07:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:01</t>
+          <t>2026-09-29 23:07:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">

--- a/etf_holdings/2026-09-29_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:56</t>
+          <t>2026-09-29 23:52:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.35%243,000</t>
+          <t>3.39%243,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:56</t>
+          <t>2026-09-29 23:52:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.20%633,000</t>
+          <t>3.19%633,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.19%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:56</t>
+          <t>2026-09-29 23:52:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.70%406,000</t>
+          <t>2.65%406,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.65%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:57</t>
+          <t>2026-09-29 23:52:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:57</t>
+          <t>2026-09-29 23:52:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.60%519,000</t>
+          <t>1.62%519,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:57</t>
+          <t>2026-09-29 23:52:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -839,12 +839,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.51%88,100</t>
+          <t>1.55%88,100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:57</t>
+          <t>2026-09-29 23:52:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -882,40 +882,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6981MURATA MANUFACTURING CO LTD</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.46%351,900</t>
+          <t>1.48%158,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>351900</v>
+        <v>158000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:57</t>
+          <t>2026-09-29 23:52:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -945,27 +945,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>6981MURATA MANUFACTURING CO LTD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4.36%3400</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.46%158,000</t>
+          <t>1.46%351,900</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -974,11 +974,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>158000</v>
+        <v>351900</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:57</t>
+          <t>2026-09-29 23:52:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.35%1,665,000</t>
+          <t>1.37%1,665,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:59</t>
+          <t>2026-09-29 23:52:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.12%348,000</t>
+          <t>1.14%348,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:59</t>
+          <t>2026-09-29 23:52:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1134,40 +1134,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>4062IBIDEN CO LTD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.32%3305</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.32%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.93%106,000</t>
+          <t>0.99%83,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>106000</v>
+        <v>83000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:59</t>
+          <t>2026-09-29 23:52:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1197,27 +1197,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.25%5185</t>
+          <t>+2.32%3305</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.25%</t>
+          <t>+2.32%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.90%60,000</t>
+          <t>0.90%106,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1226,11 +1226,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>60000</v>
+        <v>106000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:59</t>
+          <t>2026-09-29 23:52:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1260,40 +1260,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4062IBIDEN CO LTD</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.25%5185</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.87%83,000</t>
+          <t>0.86%60,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>83000</v>
+        <v>60000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:59</t>
+          <t>2026-09-29 23:52:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.80%130,000</t>
+          <t>0.79%130,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:59</t>
+          <t>2026-09-29 23:52:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:59</t>
+          <t>2026-09-29 23:52:08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.65%41,000</t>
+          <t>0.61%41,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:00</t>
+          <t>2026-09-29 23:52:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:00</t>
+          <t>2026-09-29 23:52:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.47%22,600</t>
+          <t>0.48%22,600</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K19" t="n">
